--- a/Templates-Klara/sheets-template-klara.xlsx
+++ b/Templates-Klara/sheets-template-klara.xlsx
@@ -212,11 +212,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="489260389"/>
-        <c:axId val="1444836631"/>
+        <c:axId val="1135325014"/>
+        <c:axId val="819728953"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="489260389"/>
+        <c:axId val="1135325014"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -268,10 +268,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1444836631"/>
+        <c:crossAx val="819728953"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1444836631"/>
+        <c:axId val="819728953"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -346,7 +346,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489260389"/>
+        <c:crossAx val="1135325014"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -480,11 +480,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="785818816"/>
-        <c:axId val="184176531"/>
+        <c:axId val="854022207"/>
+        <c:axId val="1964148752"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="785818816"/>
+        <c:axId val="854022207"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -536,10 +536,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="184176531"/>
+        <c:crossAx val="1964148752"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="184176531"/>
+        <c:axId val="1964148752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -614,7 +614,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="785818816"/>
+        <c:crossAx val="854022207"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
